--- a/data/trans_bre/IP2003-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 1,62</t>
+          <t>-18,09; 2,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 0,68</t>
+          <t>-22,24; 0,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 28,07</t>
+          <t>4,81; 25,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 10,72</t>
+          <t>-11,46; 11,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-84,89; 30,96</t>
+          <t>-83,79; 43,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-75,43; 9,8</t>
+          <t>-74,83; 11,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,26; 679,29</t>
+          <t>28,06; 599,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,22; 93,39</t>
+          <t>-49,14; 90,54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 17,1</t>
+          <t>-3,61; 15,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 10,74</t>
+          <t>-3,87; 10,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 3,87</t>
+          <t>-13,43; 4,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 46,51</t>
+          <t>-0,05; 47,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 89,78</t>
+          <t>-12,2; 81,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 142,33</t>
+          <t>-31,48; 165,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,49; 26,03</t>
+          <t>-58,01; 30,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 246,87</t>
+          <t>-2,44; 237,36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 15,32</t>
+          <t>-3,68; 16,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 7,81</t>
+          <t>-9,36; 7,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 10,21</t>
+          <t>-6,08; 10,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 5,86</t>
+          <t>-9,67; 5,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,92; 249,44</t>
+          <t>-32,71; 246,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,51; 136,36</t>
+          <t>-64,62; 115,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-75,98; 434,98</t>
+          <t>-80,59; 399,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,99; 131,58</t>
+          <t>-74,37; 161,75</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 18,37</t>
+          <t>-2,26; 16,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 20,27</t>
+          <t>0,72; 21,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 14,97</t>
+          <t>-7,53; 17,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,44; 4,53</t>
+          <t>-41,01; 5,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 242,93</t>
+          <t>-13,66; 229,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 219,21</t>
+          <t>-0,5; 226,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 88,02</t>
+          <t>-26,74; 105,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,48; 48,2</t>
+          <t>-91,37; 63,3</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 22,52</t>
+          <t>-6,05; 23,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 21,6</t>
+          <t>-9,39; 22,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 2,89</t>
+          <t>-20,04; 3,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 5,7</t>
+          <t>-14,92; 4,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,36; 214,77</t>
+          <t>-28,21; 209,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 162,28</t>
+          <t>-37,12; 171,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-86,49; 42,13</t>
+          <t>-85,65; 54,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-81,88; 109,7</t>
+          <t>-83,39; 86,74</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 17,46</t>
+          <t>-1,54; 16,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 20,2</t>
+          <t>-8,2; 18,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 11,93</t>
+          <t>-10,44; 10,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 5,59</t>
+          <t>-6,78; 5,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 775,4</t>
+          <t>-30,47; 622,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 222,91</t>
+          <t>-38,88; 156,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,66; 263,34</t>
+          <t>-70,27; 215,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 479,22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 8,62</t>
+          <t>-3,61; 10,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 12,2</t>
+          <t>-1,66; 12,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 4,39</t>
+          <t>-6,72; 4,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 9,74</t>
+          <t>-5,65; 9,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 125,02</t>
+          <t>-32,44; 148,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 170,67</t>
+          <t>-13,72; 168,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-58,48; 77,55</t>
+          <t>-59,58; 89,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 108,49</t>
+          <t>-36,7; 114,5</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 7,06</t>
+          <t>-5,78; 7,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 11,61</t>
+          <t>-0,52; 11,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 7,4</t>
+          <t>-4,93; 6,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 5,12</t>
+          <t>-3,14; 4,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 58,9</t>
+          <t>-31,92; 61,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 142,89</t>
+          <t>-6,12; 137,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,96; 89,89</t>
+          <t>-34,84; 77,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,37; 228,61</t>
+          <t>-58,34; 270,48</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,41</t>
+          <t>0,26; 6,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,01</t>
+          <t>0,52; 6,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,36</t>
+          <t>-2,21; 3,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 15,36</t>
+          <t>-2,72; 14,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 50,72</t>
+          <t>1,76; 54,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,98; 60,98</t>
+          <t>3,73; 56,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 28,76</t>
+          <t>-15,59; 31,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 117,94</t>
+          <t>-18,74; 109,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 2,18</t>
+          <t>-18,44; 2,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 0,58</t>
+          <t>-21,86; 2,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 25,79</t>
+          <t>4,8; 26,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 11,19</t>
+          <t>-11,66; 11,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-83,79; 43,77</t>
+          <t>-84,03; 47,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,83; 11,71</t>
+          <t>-74,92; 20,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,06; 599,18</t>
+          <t>27,14; 622,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,14; 90,54</t>
+          <t>-49,89; 98,43</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 15,37</t>
+          <t>-3,95; 17,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 10,65</t>
+          <t>-5,02; 10,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 4,53</t>
+          <t>-13,35; 4,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 47,96</t>
+          <t>-0,34; 51,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 81,07</t>
+          <t>-15,17; 89,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,48; 165,03</t>
+          <t>-37,95; 142,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 30,22</t>
+          <t>-56,36; 31,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 237,36</t>
+          <t>-4,76; 248,49</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 16,16</t>
+          <t>-4,16; 15,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 7,86</t>
+          <t>-9,01; 8,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 10,29</t>
+          <t>-5,75; 9,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 5,69</t>
+          <t>-10,29; 5,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 246,36</t>
+          <t>-30,6; 241,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,62; 115,1</t>
+          <t>-63,69; 139,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-80,59; 399,93</t>
+          <t>-78,16; 520,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,37; 161,75</t>
+          <t>-75,2; 137,59</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 16,71</t>
+          <t>-1,61; 17,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 21,61</t>
+          <t>0,54; 21,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 17,44</t>
+          <t>-8,17; 16,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 5,81</t>
+          <t>-41,65; 5,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 229,16</t>
+          <t>-11,61; 236,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 226,02</t>
+          <t>-0,62; 226,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 105,56</t>
+          <t>-29,35; 103,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,37; 63,3</t>
+          <t>-91,8; 56,81</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 23,02</t>
+          <t>-7,45; 21,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 22,61</t>
+          <t>-10,89; 20,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 3,3</t>
+          <t>-20,92; 2,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 4,74</t>
+          <t>-16,31; 4,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,21; 209,08</t>
+          <t>-34,98; 178,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 171,4</t>
+          <t>-41,32; 153,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-85,65; 54,49</t>
+          <t>-85,44; 49,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-83,39; 86,74</t>
+          <t>-82,22; 90,99</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 16,63</t>
+          <t>-1,09; 17,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 18,54</t>
+          <t>-7,18; 19,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 10,48</t>
+          <t>-9,38; 12,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 5,73</t>
+          <t>-7,33; 5,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 622,43</t>
+          <t>-29,85; 826,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 156,79</t>
+          <t>-33,04; 172,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,27; 215,56</t>
+          <t>-66,05; 275,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 479,22</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 10,1</t>
+          <t>-3,78; 9,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 12,09</t>
+          <t>-2,14; 12,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 4,97</t>
+          <t>-7,62; 4,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 9,59</t>
+          <t>-5,35; 8,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 148,26</t>
+          <t>-33,32; 158,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 168,38</t>
+          <t>-18,67; 170,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 89,32</t>
+          <t>-64,74; 75,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-36,7; 114,5</t>
+          <t>-35,16; 105,12</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 7,74</t>
+          <t>-5,34; 7,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 11,75</t>
+          <t>-0,92; 11,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 6,63</t>
+          <t>-5,02; 6,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 4,72</t>
+          <t>-3,83; 4,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 61,67</t>
+          <t>-29,39; 59,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 137,13</t>
+          <t>-6,44; 133,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 77,75</t>
+          <t>-34,05; 72,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-58,34; 270,48</t>
+          <t>-64,11; 257,02</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 6,87</t>
+          <t>0,21; 6,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 6,54</t>
+          <t>0,55; 6,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,65</t>
+          <t>-2,56; 3,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 14,44</t>
+          <t>-2,53; 14,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 54,34</t>
+          <t>0,72; 51,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 56,25</t>
+          <t>3,73; 58,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 31,91</t>
+          <t>-18,02; 33,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 109,7</t>
+          <t>-18,05; 112,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-2,89%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 2,5</t>
+          <t>-18,88; 1,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 2,15</t>
+          <t>-21,77; 0,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 26,16</t>
+          <t>4,57; 28,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 11,8</t>
+          <t>-6,38; 15,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-84,03; 47,49</t>
+          <t>-84,89; 30,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,92; 20,66</t>
+          <t>-75,43; 9,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,14; 622,89</t>
+          <t>22,26; 679,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,89; 98,43</t>
+          <t>-30,73; 131,84</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,55</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 17,14</t>
+          <t>-2,78; 17,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 10,69</t>
+          <t>-4,62; 10,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 4,63</t>
+          <t>-14,23; 3,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 51,54</t>
+          <t>-7,86; 17,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 89,89</t>
+          <t>-10,08; 89,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 142,72</t>
+          <t>-35,03; 142,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-56,36; 31,78</t>
+          <t>-58,49; 26,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 248,49</t>
+          <t>-23,98; 79,73</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-18,84%</t>
+          <t>-16,25%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 15,85</t>
+          <t>-3,67; 15,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 8,13</t>
+          <t>-9,4; 7,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 9,61</t>
+          <t>-6,12; 10,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 5,55</t>
+          <t>-8,84; 6,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,6; 241,96</t>
+          <t>-29,92; 249,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-63,69; 139,05</t>
+          <t>-64,51; 136,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 520,76</t>
+          <t>-75,98; 434,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,2; 137,59</t>
+          <t>-75,32; 147,09</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-12,08</t>
+          <t>-10,29</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-49,75%</t>
+          <t>-45,12%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 17,93</t>
+          <t>-0,95; 18,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 21,49</t>
+          <t>-0,58; 20,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 16,72</t>
+          <t>-8,97; 14,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,65; 5,13</t>
+          <t>-40,37; 5,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 236,86</t>
+          <t>-13,48; 242,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 226,34</t>
+          <t>-4,97; 219,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,35; 103,57</t>
+          <t>-30,64; 88,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,8; 56,81</t>
+          <t>-87,38; 52,68</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,68</t>
+          <t>-5,09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-37,53%</t>
+          <t>-39,49%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 21,16</t>
+          <t>-7,13; 22,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 20,59</t>
+          <t>-9,5; 21,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 2,82</t>
+          <t>-20,55; 2,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 4,16</t>
+          <t>-15,52; 5,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 178,87</t>
+          <t>-31,36; 214,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 153,95</t>
+          <t>-36,16; 162,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-85,44; 49,12</t>
+          <t>-86,49; 42,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-82,22; 90,99</t>
+          <t>-82,25; 102,04</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-14,03%</t>
+          <t>-7,08%</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 17,61</t>
+          <t>-0,7; 17,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 19,2</t>
+          <t>-5,34; 20,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 12,39</t>
+          <t>-9,76; 11,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 5,44</t>
+          <t>-6,84; 6,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 826,96</t>
+          <t>-18,5; 775,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 172,12</t>
+          <t>-24,87; 222,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,05; 275,65</t>
+          <t>-70,66; 263,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 9,43</t>
+          <t>-3,74; 8,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 12,2</t>
+          <t>-2,01; 12,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 4,17</t>
+          <t>-6,66; 4,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 8,7</t>
+          <t>-5,63; 10,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 158,84</t>
+          <t>-32,66; 125,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 170,03</t>
+          <t>-15,71; 170,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-64,74; 75,53</t>
+          <t>-58,48; 77,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 105,12</t>
+          <t>-34,56; 109,92</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 7,61</t>
+          <t>-6,3; 7,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 11,69</t>
+          <t>-0,87; 11,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 6,52</t>
+          <t>-4,79; 7,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,98</t>
+          <t>-3,89; 4,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,39; 59,7</t>
+          <t>-33,57; 58,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 133,91</t>
+          <t>-7,47; 142,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,05; 72,47</t>
+          <t>-32,96; 89,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-64,11; 257,02</t>
+          <t>-69,06; 227,63</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 6,64</t>
+          <t>0,31; 6,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,76</t>
+          <t>0,42; 7,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,77</t>
+          <t>-2,84; 3,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 14,72</t>
+          <t>-4,09; 4,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 51,27</t>
+          <t>2,03; 50,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 58,86</t>
+          <t>2,98; 60,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 33,27</t>
+          <t>-18,73; 28,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 112,29</t>
+          <t>-24,68; 36,28</t>
         </is>
       </c>
     </row>
